--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134232510</v>
+        <v>134550566</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476892</v>
+        <v>476874</v>
       </c>
       <c r="R2" t="n">
-        <v>6847037</v>
+        <v>6847026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232508</v>
+        <v>134232510</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476847</v>
+        <v>476892</v>
       </c>
       <c r="R3" t="n">
-        <v>6846940</v>
+        <v>6847037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232504</v>
+        <v>134550478</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,41 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477136</v>
+        <v>476884</v>
       </c>
       <c r="R4" t="n">
-        <v>6846947</v>
+        <v>6847049</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,17 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,60 +963,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126060736</v>
+        <v>134232508</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476799</v>
+        <v>476847</v>
       </c>
       <c r="R5" t="n">
-        <v>6847223</v>
+        <v>6846940</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,12 +1044,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,15 +1069,703 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134550324</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476834</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6847078</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134550552</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476874</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6847026</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134232504</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477136</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126060736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476799</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6847223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134552313</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477123</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6846954</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134552366</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>477122</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6846946</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134551437</v>
+      </c>
+      <c r="B12" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476928</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6847019</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,49 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134232508</v>
+        <v>135475302</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476847</v>
+        <v>476821</v>
       </c>
       <c r="R5" t="n">
-        <v>6846940</v>
+        <v>6847009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,17 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,19 +1060,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134550324</v>
+        <v>134232508</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1109,20 +1100,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476834</v>
+        <v>476847</v>
       </c>
       <c r="R6" t="n">
-        <v>6847078</v>
+        <v>6846940</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,12 +1141,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,19 +1166,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134550552</v>
+        <v>134550324</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476874</v>
+        <v>476834</v>
       </c>
       <c r="R7" t="n">
-        <v>6847026</v>
+        <v>6847078</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,49 +1275,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134232504</v>
+        <v>134550552</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477136</v>
+        <v>476874</v>
       </c>
       <c r="R8" t="n">
-        <v>6846947</v>
+        <v>6847026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,17 +1340,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,60 +1360,64 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126060736</v>
+        <v>134232504</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476799</v>
+        <v>477136</v>
       </c>
       <c r="R9" t="n">
-        <v>6847223</v>
+        <v>6846947</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1446,12 +1441,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,22 +1466,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134552313</v>
+        <v>126060736</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477123</v>
+        <v>476799</v>
       </c>
       <c r="R10" t="n">
-        <v>6846954</v>
+        <v>6847223</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,7 +1575,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134552366</v>
+        <v>134552313</v>
       </c>
       <c r="B11" t="n">
         <v>99112</v>
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477122</v>
+        <v>477123</v>
       </c>
       <c r="R11" t="n">
-        <v>6846946</v>
+        <v>6846954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134551437</v>
+        <v>134552366</v>
       </c>
       <c r="B12" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476928</v>
+        <v>477122</v>
       </c>
       <c r="R12" t="n">
-        <v>6847019</v>
+        <v>6846946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1766,103 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134551437</v>
+      </c>
+      <c r="B13" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476928</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6847019</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134550566</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134550478</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475302</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232508</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134550324</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134550552</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232504</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060736</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134552313</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134552366</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,8 +1923,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134551437</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>135475302</v>
       </c>
       <c r="B5" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>135475302</v>
       </c>
       <c r="B5" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27600-2026 artfynd.xlsx
+++ b/artfynd/A 27600-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,49 +995,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134232508</v>
+        <v>135475302</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>80557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476847</v>
+        <v>476821</v>
       </c>
       <c r="R5" t="n">
-        <v>6846940</v>
+        <v>6847009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,17 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,24 +1080,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232508</t>
+          <t>https://artportalen.se/Sighting/135475302</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134550324</v>
+        <v>134232508</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1134,20 +1125,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476834</v>
+        <v>476847</v>
       </c>
       <c r="R6" t="n">
-        <v>6847078</v>
+        <v>6846940</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,12 +1166,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,24 +1191,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134550324</t>
+          <t>https://artportalen.se/Sighting/134232508</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134550552</v>
+        <v>134550324</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476874</v>
+        <v>476834</v>
       </c>
       <c r="R7" t="n">
-        <v>6847026</v>
+        <v>6847078</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,55 +1304,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134550552</t>
+          <t>https://artportalen.se/Sighting/134550324</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134232504</v>
+        <v>134550552</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477136</v>
+        <v>476874</v>
       </c>
       <c r="R8" t="n">
-        <v>6846947</v>
+        <v>6847026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,17 +1375,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,65 +1395,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232504</t>
+          <t>https://artportalen.se/Sighting/134550552</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126060736</v>
+        <v>134232504</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476799</v>
+        <v>477136</v>
       </c>
       <c r="R9" t="n">
-        <v>6847223</v>
+        <v>6846947</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,12 +1481,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,27 +1506,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126060736</t>
+          <t>https://artportalen.se/Sighting/134232504</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134552313</v>
+        <v>126060736</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477123</v>
+        <v>476799</v>
       </c>
       <c r="R10" t="n">
-        <v>6846954</v>
+        <v>6847223</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,13 +1619,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134552313</t>
+          <t>https://artportalen.se/Sighting/126060736</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134552366</v>
+        <v>134552313</v>
       </c>
       <c r="B11" t="n">
         <v>99112</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477122</v>
+        <v>477123</v>
       </c>
       <c r="R11" t="n">
-        <v>6846946</v>
+        <v>6846954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,16 +1721,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134552366</t>
+          <t>https://artportalen.se/Sighting/134552313</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134551437</v>
+        <v>134552366</v>
       </c>
       <c r="B12" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476928</v>
+        <v>477122</v>
       </c>
       <c r="R12" t="n">
-        <v>6847019</v>
+        <v>6846946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,6 +1822,108 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134552366</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134551437</v>
+      </c>
+      <c r="B13" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476928</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6847019</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134551437</t>
         </is>
@@ -1840,6 +1942,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
